--- a/outputs/06_测试数据/发动机主线业务流程-多工厂一级工艺版/导入包/产品与工艺_模板.xlsx
+++ b/outputs/06_测试数据/发动机主线业务流程-多工厂一级工艺版/导入包/产品与工艺_模板.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="B2" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C2" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D2" s="32" t="inlineStr">
@@ -795,12 +795,12 @@
       </c>
       <c r="E2" s="32" t="inlineStr">
         <is>
-          <t>核对毛坯状态</t>
+          <t>确认机匣组件计划</t>
         </is>
       </c>
       <c r="F2" s="32" t="inlineStr">
         <is>
-          <t>核对机匣毛坯批次、状态和余量。</t>
+          <t>确认机加厂子生产订单、数量与交付节拍。</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D3" s="32" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="E3" s="32" t="inlineStr">
         <is>
-          <t>装夹找正</t>
+          <t>接收机匣组件完工反馈</t>
         </is>
       </c>
       <c r="F3" s="32" t="inlineStr">
         <is>
-          <t>完成机匣毛坯装夹、找正和程序确认。</t>
+          <t>接收并确认机匣组件完工状态。</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D4" s="32" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="E4" s="32" t="inlineStr">
         <is>
-          <t>执行五轴加工</t>
+          <t>确认盘轴组件计划</t>
         </is>
       </c>
       <c r="F4" s="32" t="inlineStr">
         <is>
-          <t>完成关键孔面与安装面粗精加工。</t>
+          <t>确认盘轴厂子生产订单、数量与交付节拍。</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="E5" s="32" t="inlineStr">
         <is>
-          <t>清理去毛刺</t>
+          <t>接收盘轴组件完工反馈</t>
         </is>
       </c>
       <c r="F5" s="32" t="inlineStr">
         <is>
-          <t>完成机加后清理和去毛刺。</t>
+          <t>接收并确认盘轴组件完工状态。</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
-          <t>三坐标检测</t>
+          <t>确认叶片组件计划</t>
         </is>
       </c>
       <c r="F6" s="32" t="inlineStr">
         <is>
-          <t>完成关键尺寸和安装面的三坐标检测。</t>
+          <t>确认叶片厂子生产订单、数量与交付节拍。</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="E7" s="32" t="inlineStr">
         <is>
-          <t>放行判定</t>
+          <t>接收叶片组件完工反馈</t>
         </is>
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>形成机匣完件放行结论。</t>
+          <t>接收并确认叶片组件套完工状态。</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
-          <t>复合加工准备</t>
+          <t>确认装配厂计划</t>
         </is>
       </c>
       <c r="F8" s="32" t="inlineStr">
         <is>
-          <t>核对盘轴锻件状态并完成装夹。</t>
+          <t>确认装配厂子生产订单、正式工艺路线与释放条件。</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D9" s="32" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
-          <t>盘轴车铣加工</t>
+          <t>接收装配完工反馈</t>
         </is>
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>完成盘轴关键面和接口加工。</t>
+          <t>接收并确认装配、试车、入库与交付状态。</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
-          <t>执行动平衡检测</t>
+          <t>毛坯核对</t>
         </is>
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>完成盘轴动平衡初检与偏差记录。</t>
+          <t>核对机匣毛坯批次与状态。</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>配重修正</t>
+          <t>粗加工</t>
         </is>
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>完成配重修正和复核。</t>
+          <t>完成关键孔面与外形粗加工。</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B12" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
-          <t>无损检测</t>
+          <t>精加工关键面</t>
         </is>
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>完成盘轴无损探伤和记录。</t>
+          <t>完成机匣关键孔面与安装面精加工。</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
-          <t>尺寸外观判定</t>
+          <t>清理去毛刺</t>
         </is>
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>完成盘轴尺寸、外观和放行判定。</t>
+          <t>完成清理、去毛刺和外观复核。</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="D14" s="32" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="E14" s="32" t="inlineStr">
         <is>
-          <t>叶片基准定位</t>
+          <t>三坐标检测</t>
         </is>
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>完成叶片毛坯定位和程序确认。</t>
+          <t>完成关键尺寸与同轴度检测。</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
-          <t>型面成型</t>
+          <t>终检放行</t>
         </is>
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>完成叶片型面加工和冷端修整。</t>
+          <t>形成机匣组件终检结论。</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B16" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="E16" s="32" t="inlineStr">
         <is>
-          <t>涂层前处理</t>
+          <t>毛坯装夹</t>
         </is>
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>完成叶片表面清洁和遮蔽处理。</t>
+          <t>完成盘轴毛坯装夹和基准确认。</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B17" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D17" s="32" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="E17" s="32" t="inlineStr">
         <is>
-          <t>喷涂固化</t>
+          <t>车铣复合加工</t>
         </is>
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
-          <t>完成涂层喷涂、固化和冷却。</t>
+          <t>完成盘轴关键面复合加工。</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D18" s="32" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="E18" s="32" t="inlineStr">
         <is>
-          <t>型面与流道检测</t>
+          <t>动平衡检测</t>
         </is>
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>完成叶片型面和通流复核。</t>
+          <t>完成盘轴动平衡检测。</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D19" s="32" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>外观放行</t>
+          <t>配重修正</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>完成叶片外观复核和放行。</t>
+          <t>完成配重调整和复测。</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="D20" s="32" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>关键件齐套复核</t>
+          <t>无损检测</t>
         </is>
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
-          <t>复核机匣件、盘轴模块和叶片组件到位。</t>
+          <t>完成盘轴探伤与尺寸检查。</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="D21" s="32" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>装配配套确认</t>
+          <t>终检放行</t>
         </is>
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>确认紧固件和密封件配套齐全。</t>
+          <t>形成盘轴组件终检结论。</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B22" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D22" s="32" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="E22" s="32" t="inlineStr">
         <is>
-          <t>核心机装配</t>
+          <t>型面定位</t>
         </is>
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
-          <t>完成机匣、盘轴和叶片关键部位总装。</t>
+          <t>完成叶片毛坯定位与程序确认。</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B23" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D23" s="32" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>联接复核</t>
+          <t>成型修整</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>完成关键联接点力矩和状态复核。</t>
+          <t>完成叶片型面成型与冷端修整。</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B24" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D24" s="32" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t>执行整机试车</t>
+          <t>表面前处理</t>
         </is>
       </c>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t>完成整机试车与关键参数采集。</t>
+          <t>完成表面清洁与前处理。</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D25" s="32" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>交付放行</t>
+          <t>喷涂固化</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>完成质量结论、包装确认和交付放行。</t>
+          <t>完成保护涂层喷涂与固化。</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B26" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="D26" s="32" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="E26" s="32" t="inlineStr">
         <is>
-          <t>确认阶段产能</t>
+          <t>型面检测</t>
         </is>
       </c>
       <c r="F26" s="32" t="inlineStr">
         <is>
-          <t>按10-机加厂阶段完成对应工厂产能确认阶段排产与执行状态</t>
+          <t>完成型面、流道与外观复核。</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B27" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="D27" s="32" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="E27" s="32" t="inlineStr">
         <is>
-          <t>完成阶段交付</t>
+          <t>终检放行</t>
         </is>
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>完成10-机加厂阶段完成并更新项目部一级协同节点状态</t>
+          <t>形成叶片组件套终检结论。</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B28" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D28" s="32" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="E28" s="32" t="inlineStr">
         <is>
-          <t>确认阶段产能</t>
+          <t>核对装配齐套</t>
         </is>
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>按20-盘轴厂阶段完成对应工厂产能确认阶段排产与执行状态</t>
+          <t>核对机匣组件、盘轴组件和叶片组件套。</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B29" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D29" s="32" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>完成阶段交付</t>
+          <t>装配工位准备</t>
         </is>
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>完成20-盘轴厂阶段完成并更新项目部一级协同节点状态</t>
+          <t>确认工位、工具、SOP 与质量前置条件。</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D30" s="32" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="E30" s="32" t="inlineStr">
         <is>
-          <t>确认阶段产能</t>
+          <t>ST20-01 机匣定位</t>
         </is>
       </c>
       <c r="F30" s="32" t="inlineStr">
         <is>
-          <t>按30-叶片厂阶段完成对应工厂产能确认阶段排产与执行状态</t>
+          <t>完成机匣定位与装配基准确认。</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B31" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D31" s="32" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>完成阶段交付</t>
+          <t>ST20-02 盘轴装配</t>
         </is>
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>完成30-叶片厂阶段完成并更新项目部一级协同节点状态</t>
+          <t>完成盘轴装配与关键连接紧固。</t>
         </is>
       </c>
     </row>
@@ -1740,27 +1740,27 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D32" s="32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E32" s="32" t="inlineStr">
         <is>
-          <t>确认阶段产能</t>
+          <t>ST20-03 叶片组件装配</t>
         </is>
       </c>
       <c r="F32" s="32" t="inlineStr">
         <is>
-          <t>按40-装配厂总装试车完成对应工厂产能确认阶段排产与执行状态</t>
+          <t>完成叶片组件装配与间隙复核。</t>
         </is>
       </c>
     </row>
@@ -1772,37 +1772,61 @@
       </c>
       <c r="B33" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="D33" s="32" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>完工复核</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>完成关键连接复核与状态确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>A.01</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>RT-ASM-ENG-A1000-V1</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
-        <is>
-          <t>完成阶段交付</t>
-        </is>
-      </c>
-      <c r="F33" s="32" t="inlineStr">
-        <is>
-          <t>完成40-装配厂总装试车完成并更新项目部一级协同节点状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="32" t="inlineStr"/>
-      <c r="B34" s="32" t="inlineStr"/>
-      <c r="C34" s="32" t="inlineStr"/>
-      <c r="D34" s="32" t="inlineStr"/>
-      <c r="E34" s="32" t="inlineStr"/>
-      <c r="F34" s="32" t="inlineStr"/>
+      <c r="E34" s="32" t="inlineStr">
+        <is>
+          <t>入库准备</t>
+        </is>
+      </c>
+      <c r="F34" s="32" t="inlineStr">
+        <is>
+          <t>完成入库前标签、批次和状态准备。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="32" t="inlineStr"/>
@@ -3176,28 +3200,28 @@
       </c>
       <c r="B2" s="32" t="inlineStr">
         <is>
-          <t>机匣毛坯</t>
+          <t>机匣毛坯件</t>
         </is>
       </c>
       <c r="C2" s="32" t="inlineStr">
         <is>
-          <t>零部件</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="D2" s="32" t="inlineStr">
         <is>
-          <t>AE-100-001</t>
+          <t>A1000-CAS-BLK</t>
         </is>
       </c>
       <c r="E2" s="32" t="inlineStr"/>
       <c r="F2" s="32" t="inlineStr">
         <is>
-          <t>机匣毛坯件</t>
+          <t>机匣毛坯</t>
         </is>
       </c>
       <c r="G2" s="32" t="inlineStr">
         <is>
-          <t>自制件</t>
+          <t>外购件</t>
         </is>
       </c>
       <c r="H2" s="32" t="inlineStr">
@@ -3207,7 +3231,7 @@
       </c>
       <c r="I2" s="32" t="inlineStr">
         <is>
-          <t>关键件</t>
+          <t>重要件</t>
         </is>
       </c>
       <c r="J2" s="32" t="inlineStr">
@@ -3241,12 +3265,12 @@
       </c>
       <c r="W2" s="32" t="inlineStr">
         <is>
-          <t>Mat001</t>
+          <t>MAT-CAS-BLANK-001</t>
         </is>
       </c>
       <c r="X2" s="32" t="inlineStr">
         <is>
-          <t>机加厂输入件</t>
+          <t>机加厂输入件。</t>
         </is>
       </c>
       <c r="Y2" s="32" t="inlineStr">
@@ -3261,7 +3285,7 @@
       </c>
       <c r="AA2" s="32" t="inlineStr">
         <is>
-          <t>Mat001</t>
+          <t>MAT-CAS-BLANK-001</t>
         </is>
       </c>
       <c r="AB2" s="32" t="inlineStr"/>
@@ -3274,28 +3298,28 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>机匣机加完件</t>
+          <t>盘轴毛坯件</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
         <is>
-          <t>零部件</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>AE-100-002</t>
+          <t>A1000-SHAFT-BLK</t>
         </is>
       </c>
       <c r="E3" s="32" t="inlineStr"/>
       <c r="F3" s="32" t="inlineStr">
         <is>
-          <t>机加阶段完成件</t>
+          <t>盘轴毛坯</t>
         </is>
       </c>
       <c r="G3" s="32" t="inlineStr">
         <is>
-          <t>自制件</t>
+          <t>外购件</t>
         </is>
       </c>
       <c r="H3" s="32" t="inlineStr">
@@ -3305,7 +3329,7 @@
       </c>
       <c r="I3" s="32" t="inlineStr">
         <is>
-          <t>关键件</t>
+          <t>重要件</t>
         </is>
       </c>
       <c r="J3" s="32" t="inlineStr">
@@ -3339,12 +3363,12 @@
       </c>
       <c r="W3" s="32" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-SHAFT-BLANK-001</t>
         </is>
       </c>
       <c r="X3" s="32" t="inlineStr">
         <is>
-          <t>10-机加厂正式工艺产出物</t>
+          <t>盘轴厂输入件。</t>
         </is>
       </c>
       <c r="Y3" s="32" t="inlineStr">
@@ -3359,7 +3383,7 @@
       </c>
       <c r="AA3" s="32" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-SHAFT-BLANK-001</t>
         </is>
       </c>
       <c r="AB3" s="32" t="inlineStr"/>
@@ -3372,28 +3396,28 @@
       </c>
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>盘轴锻件</t>
+          <t>叶片毛坯件</t>
         </is>
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>零部件</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="D4" s="32" t="inlineStr">
         <is>
-          <t>AE-100-003</t>
+          <t>A1000-BLADE-BLK</t>
         </is>
       </c>
       <c r="E4" s="32" t="inlineStr"/>
       <c r="F4" s="32" t="inlineStr">
         <is>
-          <t>盘轴毛坯件</t>
+          <t>叶片毛坯</t>
         </is>
       </c>
       <c r="G4" s="32" t="inlineStr">
         <is>
-          <t>自制件</t>
+          <t>外购件</t>
         </is>
       </c>
       <c r="H4" s="32" t="inlineStr">
@@ -3403,7 +3427,7 @@
       </c>
       <c r="I4" s="32" t="inlineStr">
         <is>
-          <t>关键件</t>
+          <t>一般件</t>
         </is>
       </c>
       <c r="J4" s="32" t="inlineStr">
@@ -3437,12 +3461,12 @@
       </c>
       <c r="W4" s="32" t="inlineStr">
         <is>
-          <t>Mat003</t>
+          <t>MAT-BLADE-BLANK-001</t>
         </is>
       </c>
       <c r="X4" s="32" t="inlineStr">
         <is>
-          <t>盘轴厂输入件</t>
+          <t>叶片厂输入件。</t>
         </is>
       </c>
       <c r="Y4" s="32" t="inlineStr">
@@ -3457,7 +3481,7 @@
       </c>
       <c r="AA4" s="32" t="inlineStr">
         <is>
-          <t>Mat003</t>
+          <t>MAT-BLADE-BLANK-001</t>
         </is>
       </c>
       <c r="AB4" s="32" t="inlineStr"/>
@@ -3470,28 +3494,28 @@
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>盘轴模块</t>
+          <t>叶片涂层辅料</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>零部件</t>
+          <t>辅助材料</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>AE-100-004</t>
+          <t>A1000-COAT-001</t>
         </is>
       </c>
       <c r="E5" s="32" t="inlineStr"/>
       <c r="F5" s="32" t="inlineStr">
         <is>
-          <t>盘轴阶段完成件</t>
+          <t>叶片保护涂层辅料</t>
         </is>
       </c>
       <c r="G5" s="32" t="inlineStr">
         <is>
-          <t>自制件</t>
+          <t>外购件</t>
         </is>
       </c>
       <c r="H5" s="32" t="inlineStr">
@@ -3501,7 +3525,7 @@
       </c>
       <c r="I5" s="32" t="inlineStr">
         <is>
-          <t>关键件</t>
+          <t>一般件</t>
         </is>
       </c>
       <c r="J5" s="32" t="inlineStr">
@@ -3535,12 +3559,12 @@
       </c>
       <c r="W5" s="32" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-COAT-001</t>
         </is>
       </c>
       <c r="X5" s="32" t="inlineStr">
         <is>
-          <t>20-盘轴厂正式工艺产出物</t>
+          <t>叶片组件涂层处理耗材。</t>
         </is>
       </c>
       <c r="Y5" s="32" t="inlineStr">
@@ -3555,7 +3579,7 @@
       </c>
       <c r="AA5" s="32" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-COAT-001</t>
         </is>
       </c>
       <c r="AB5" s="32" t="inlineStr"/>
@@ -3568,7 +3592,7 @@
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>叶片毛坯</t>
+          <t>机匣组件</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -3578,13 +3602,13 @@
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>AE-100-005</t>
+          <t>A1000-CAS-001</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr"/>
       <c r="F6" s="32" t="inlineStr">
         <is>
-          <t>叶片毛坯件</t>
+          <t>机匣组件</t>
         </is>
       </c>
       <c r="G6" s="32" t="inlineStr">
@@ -3599,7 +3623,7 @@
       </c>
       <c r="I6" s="32" t="inlineStr">
         <is>
-          <t>重要件</t>
+          <t>关键件</t>
         </is>
       </c>
       <c r="J6" s="32" t="inlineStr">
@@ -3633,12 +3657,12 @@
       </c>
       <c r="W6" s="32" t="inlineStr">
         <is>
-          <t>Mat005</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="X6" s="32" t="inlineStr">
         <is>
-          <t>叶片厂输入件</t>
+          <t>用于装配领料。</t>
         </is>
       </c>
       <c r="Y6" s="32" t="inlineStr">
@@ -3653,7 +3677,7 @@
       </c>
       <c r="AA6" s="32" t="inlineStr">
         <is>
-          <t>Mat005</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="AB6" s="32" t="inlineStr"/>
@@ -3666,7 +3690,7 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>叶片组件</t>
+          <t>盘轴组件</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -3676,13 +3700,13 @@
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>AE-100-006</t>
+          <t>A1000-SHAFT-001</t>
         </is>
       </c>
       <c r="E7" s="32" t="inlineStr"/>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>叶片阶段完成件</t>
+          <t>盘轴组件</t>
         </is>
       </c>
       <c r="G7" s="32" t="inlineStr">
@@ -3731,12 +3755,12 @@
       </c>
       <c r="W7" s="32" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="X7" s="32" t="inlineStr">
         <is>
-          <t>30-叶片厂正式工艺产出物</t>
+          <t>用于装配领料。</t>
         </is>
       </c>
       <c r="Y7" s="32" t="inlineStr">
@@ -3751,7 +3775,7 @@
       </c>
       <c r="AA7" s="32" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="AB7" s="32" t="inlineStr"/>
@@ -3764,28 +3788,28 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>紧固件标准包</t>
+          <t>叶片组件套</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>配套件</t>
+          <t>零部件</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>AE-100-007</t>
+          <t>A1000-BLADESET-001</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr"/>
       <c r="F8" s="32" t="inlineStr">
         <is>
-          <t>总装标准件包</t>
+          <t>叶片组件套</t>
         </is>
       </c>
       <c r="G8" s="32" t="inlineStr">
         <is>
-          <t>外购件</t>
+          <t>自制件</t>
         </is>
       </c>
       <c r="H8" s="32" t="inlineStr">
@@ -3795,7 +3819,7 @@
       </c>
       <c r="I8" s="32" t="inlineStr">
         <is>
-          <t>一般件</t>
+          <t>关键件</t>
         </is>
       </c>
       <c r="J8" s="32" t="inlineStr">
@@ -3829,12 +3853,12 @@
       </c>
       <c r="W8" s="32" t="inlineStr">
         <is>
-          <t>Mat007</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="X8" s="32" t="inlineStr">
         <is>
-          <t>总装工位标准件</t>
+          <t>用于装配领料。</t>
         </is>
       </c>
       <c r="Y8" s="32" t="inlineStr">
@@ -3849,7 +3873,7 @@
       </c>
       <c r="AA8" s="32" t="inlineStr">
         <is>
-          <t>Mat007</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="AB8" s="32" t="inlineStr"/>
@@ -3862,28 +3886,32 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>密封垫组件</t>
+          <t>航发总成A1000</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>配套件</t>
+          <t>零部件</t>
         </is>
       </c>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>AE-100-008</t>
-        </is>
-      </c>
-      <c r="E9" s="32" t="inlineStr"/>
+          <t>A1000-ENG-001</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>A1000</t>
+        </is>
+      </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>总装密封件</t>
+          <t>发动机总成</t>
         </is>
       </c>
       <c r="G9" s="32" t="inlineStr">
         <is>
-          <t>外购件</t>
+          <t>自制件</t>
         </is>
       </c>
       <c r="H9" s="32" t="inlineStr">
@@ -3893,7 +3921,7 @@
       </c>
       <c r="I9" s="32" t="inlineStr">
         <is>
-          <t>重要件</t>
+          <t>关键件</t>
         </is>
       </c>
       <c r="J9" s="32" t="inlineStr">
@@ -3903,7 +3931,7 @@
       </c>
       <c r="K9" s="32" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L9" s="32" t="inlineStr"/>
@@ -3927,12 +3955,12 @@
       </c>
       <c r="W9" s="32" t="inlineStr">
         <is>
-          <t>Mat008</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="X9" s="32" t="inlineStr">
         <is>
-          <t>总装密封组件</t>
+          <t>主线场景最终交付物。</t>
         </is>
       </c>
       <c r="Y9" s="32" t="inlineStr">
@@ -3947,7 +3975,7 @@
       </c>
       <c r="AA9" s="32" t="inlineStr">
         <is>
-          <t>Mat008</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="AB9" s="32" t="inlineStr"/>
@@ -3960,23 +3988,23 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>叶片涂层辅料</t>
+          <t>总装标准件包</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>辅助材料</t>
+          <t>配套件</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>AE-100-009</t>
+          <t>A1000-STD-001</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr"/>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>叶片保护涂层</t>
+          <t>紧固件标准包</t>
         </is>
       </c>
       <c r="G10" s="32" t="inlineStr">
@@ -4025,12 +4053,12 @@
       </c>
       <c r="W10" s="32" t="inlineStr">
         <is>
-          <t>Mat009</t>
+          <t>MAT-STD-001</t>
         </is>
       </c>
       <c r="X10" s="32" t="inlineStr">
         <is>
-          <t>叶片厂涂层辅料</t>
+          <t>装配辅助标准件。</t>
         </is>
       </c>
       <c r="Y10" s="32" t="inlineStr">
@@ -4045,7 +4073,7 @@
       </c>
       <c r="AA10" s="32" t="inlineStr">
         <is>
-          <t>Mat009</t>
+          <t>MAT-STD-001</t>
         </is>
       </c>
       <c r="AB10" s="32" t="inlineStr"/>
@@ -4058,23 +4086,23 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>试车介质包</t>
+          <t>密封组件包</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>辅助材料</t>
+          <t>配套件</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>AE-100-010</t>
+          <t>A1000-SEAL-001</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr"/>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>整机试车介质</t>
+          <t>密封组件</t>
         </is>
       </c>
       <c r="G11" s="32" t="inlineStr">
@@ -4089,7 +4117,7 @@
       </c>
       <c r="I11" s="32" t="inlineStr">
         <is>
-          <t>一般件</t>
+          <t>重要件</t>
         </is>
       </c>
       <c r="J11" s="32" t="inlineStr">
@@ -4123,12 +4151,12 @@
       </c>
       <c r="W11" s="32" t="inlineStr">
         <is>
-          <t>Mat010</t>
+          <t>MAT-SEAL-001</t>
         </is>
       </c>
       <c r="X11" s="32" t="inlineStr">
         <is>
-          <t>装配厂试车耗材</t>
+          <t>装配密封类辅件。</t>
         </is>
       </c>
       <c r="Y11" s="32" t="inlineStr">
@@ -4143,67 +4171,23 @@
       </c>
       <c r="AA11" s="32" t="inlineStr">
         <is>
-          <t>Mat010</t>
+          <t>MAT-SEAL-001</t>
         </is>
       </c>
       <c r="AB11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>物料</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>航空发动机总成</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>零部件</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>AE-100-011</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>AE-100</t>
-        </is>
-      </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>整机成品</t>
-        </is>
-      </c>
-      <c r="G12" s="32" t="inlineStr">
-        <is>
-          <t>自制件</t>
-        </is>
-      </c>
-      <c r="H12" s="32" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="I12" s="32" t="inlineStr">
-        <is>
-          <t>关键件</t>
-        </is>
-      </c>
-      <c r="J12" s="32" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K12" s="32" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="A12" s="32" t="inlineStr"/>
+      <c r="B12" s="32" t="inlineStr"/>
+      <c r="C12" s="32" t="inlineStr"/>
+      <c r="D12" s="32" t="inlineStr"/>
+      <c r="E12" s="32" t="inlineStr"/>
+      <c r="F12" s="32" t="inlineStr"/>
+      <c r="G12" s="32" t="inlineStr"/>
+      <c r="H12" s="32" t="inlineStr"/>
+      <c r="I12" s="32" t="inlineStr"/>
+      <c r="J12" s="32" t="inlineStr"/>
+      <c r="K12" s="32" t="inlineStr"/>
       <c r="L12" s="32" t="inlineStr"/>
       <c r="M12" s="32" t="inlineStr"/>
       <c r="N12" s="32" t="inlineStr"/>
@@ -4213,95 +4197,27 @@
       <c r="R12" s="32" t="inlineStr"/>
       <c r="S12" s="32" t="inlineStr"/>
       <c r="T12" s="32" t="inlineStr"/>
-      <c r="U12" s="32" t="inlineStr">
-        <is>
-          <t>量产</t>
-        </is>
-      </c>
-      <c r="V12" s="32" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="W12" s="32" t="inlineStr">
-        <is>
-          <t>Mat011</t>
-        </is>
-      </c>
-      <c r="X12" s="32" t="inlineStr">
-        <is>
-          <t>发动机主线业务流程最终交付物</t>
-        </is>
-      </c>
-      <c r="Y12" s="32" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
-      <c r="Z12" s="32" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="AA12" s="32" t="inlineStr">
-        <is>
-          <t>Mat011</t>
-        </is>
-      </c>
+      <c r="U12" s="32" t="inlineStr"/>
+      <c r="V12" s="32" t="inlineStr"/>
+      <c r="W12" s="32" t="inlineStr"/>
+      <c r="X12" s="32" t="inlineStr"/>
+      <c r="Y12" s="32" t="inlineStr"/>
+      <c r="Z12" s="32" t="inlineStr"/>
+      <c r="AA12" s="32" t="inlineStr"/>
       <c r="AB12" s="32" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>物料</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>发运包装组件</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="inlineStr">
-        <is>
-          <t>配套件</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>AE-100-012</t>
-        </is>
-      </c>
+      <c r="A13" s="32" t="inlineStr"/>
+      <c r="B13" s="32" t="inlineStr"/>
+      <c r="C13" s="32" t="inlineStr"/>
+      <c r="D13" s="32" t="inlineStr"/>
       <c r="E13" s="32" t="inlineStr"/>
-      <c r="F13" s="32" t="inlineStr">
-        <is>
-          <t>发运包装辅件</t>
-        </is>
-      </c>
-      <c r="G13" s="32" t="inlineStr">
-        <is>
-          <t>外购件</t>
-        </is>
-      </c>
-      <c r="H13" s="32" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="I13" s="32" t="inlineStr">
-        <is>
-          <t>一般件</t>
-        </is>
-      </c>
-      <c r="J13" s="32" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K13" s="32" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="F13" s="32" t="inlineStr"/>
+      <c r="G13" s="32" t="inlineStr"/>
+      <c r="H13" s="32" t="inlineStr"/>
+      <c r="I13" s="32" t="inlineStr"/>
+      <c r="J13" s="32" t="inlineStr"/>
+      <c r="K13" s="32" t="inlineStr"/>
       <c r="L13" s="32" t="inlineStr"/>
       <c r="M13" s="32" t="inlineStr"/>
       <c r="N13" s="32" t="inlineStr"/>
@@ -4311,41 +4227,13 @@
       <c r="R13" s="32" t="inlineStr"/>
       <c r="S13" s="32" t="inlineStr"/>
       <c r="T13" s="32" t="inlineStr"/>
-      <c r="U13" s="32" t="inlineStr">
-        <is>
-          <t>量产</t>
-        </is>
-      </c>
-      <c r="V13" s="32" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="W13" s="32" t="inlineStr">
-        <is>
-          <t>Mat012</t>
-        </is>
-      </c>
-      <c r="X13" s="32" t="inlineStr">
-        <is>
-          <t>整机交付包装材料</t>
-        </is>
-      </c>
-      <c r="Y13" s="32" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
-      <c r="Z13" s="32" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="AA13" s="32" t="inlineStr">
-        <is>
-          <t>Mat012</t>
-        </is>
-      </c>
+      <c r="U13" s="32" t="inlineStr"/>
+      <c r="V13" s="32" t="inlineStr"/>
+      <c r="W13" s="32" t="inlineStr"/>
+      <c r="X13" s="32" t="inlineStr"/>
+      <c r="Y13" s="32" t="inlineStr"/>
+      <c r="Z13" s="32" t="inlineStr"/>
+      <c r="AA13" s="32" t="inlineStr"/>
       <c r="AB13" s="32" t="inlineStr"/>
     </row>
     <row r="14">
@@ -7751,7 +7639,7 @@
       </c>
       <c r="B2" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="C2" s="32" t="inlineStr">
@@ -7761,7 +7649,7 @@
       </c>
       <c r="D2" s="32" t="inlineStr">
         <is>
-          <t>Mb001</t>
+          <t>MBOM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="E2" s="32" t="inlineStr"/>
@@ -7772,7 +7660,7 @@
       </c>
       <c r="G2" s="32" t="inlineStr">
         <is>
-          <t>航空发动机总成MBOM</t>
+          <t>航发总成A1000 MBOM</t>
         </is>
       </c>
       <c r="H2" s="32" t="inlineStr">
@@ -7782,7 +7670,7 @@
       </c>
       <c r="I2" s="32" t="inlineStr">
         <is>
-          <t>Mb001</t>
+          <t>MBOM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="J2" s="32" t="inlineStr"/>
@@ -9115,17 +9003,17 @@
       <c r="B2" s="32" t="inlineStr"/>
       <c r="C2" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="D2" s="32" t="inlineStr">
         <is>
-          <t>航空发动机总成</t>
+          <t>航发总成A1000</t>
         </is>
       </c>
       <c r="E2" s="32" t="inlineStr">
         <is>
-          <t>AE-100-011</t>
+          <t>A1000-ENG-001</t>
         </is>
       </c>
       <c r="F2" s="32" t="inlineStr">
@@ -9167,7 +9055,7 @@
       </c>
       <c r="Q2" s="32" t="inlineStr">
         <is>
-          <t>Mb001</t>
+          <t>MBOM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="R2" s="32" t="inlineStr">
@@ -9179,7 +9067,7 @@
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="B3" s="32" t="inlineStr">
@@ -9189,17 +9077,17 @@
       </c>
       <c r="C3" s="32" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>机匣机加完件</t>
+          <t>机匣组件</t>
         </is>
       </c>
       <c r="E3" s="32" t="inlineStr">
         <is>
-          <t>AE-100-002</t>
+          <t>A1000-CAS-001</t>
         </is>
       </c>
       <c r="F3" s="32" t="inlineStr">
@@ -9241,7 +9129,7 @@
       </c>
       <c r="Q3" s="32" t="inlineStr">
         <is>
-          <t>Mb001</t>
+          <t>MBOM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="R3" s="32" t="inlineStr">
@@ -9253,7 +9141,7 @@
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="B4" s="32" t="inlineStr">
@@ -9263,17 +9151,17 @@
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="D4" s="32" t="inlineStr">
         <is>
-          <t>盘轴模块</t>
+          <t>盘轴组件</t>
         </is>
       </c>
       <c r="E4" s="32" t="inlineStr">
         <is>
-          <t>AE-100-004</t>
+          <t>A1000-SHAFT-001</t>
         </is>
       </c>
       <c r="F4" s="32" t="inlineStr">
@@ -9315,7 +9203,7 @@
       </c>
       <c r="Q4" s="32" t="inlineStr">
         <is>
-          <t>Mb001</t>
+          <t>MBOM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="R4" s="32" t="inlineStr">
@@ -9327,7 +9215,7 @@
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="B5" s="32" t="inlineStr">
@@ -9337,17 +9225,17 @@
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>叶片组件</t>
+          <t>叶片组件套</t>
         </is>
       </c>
       <c r="E5" s="32" t="inlineStr">
         <is>
-          <t>AE-100-006</t>
+          <t>A1000-BLADESET-001</t>
         </is>
       </c>
       <c r="F5" s="32" t="inlineStr">
@@ -9366,7 +9254,7 @@
         </is>
       </c>
       <c r="I5" s="32" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J5" s="32" t="inlineStr">
         <is>
@@ -9389,7 +9277,7 @@
       </c>
       <c r="Q5" s="32" t="inlineStr">
         <is>
-          <t>Mb001</t>
+          <t>MBOM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="R5" s="32" t="inlineStr">
@@ -9401,7 +9289,7 @@
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="B6" s="32" t="inlineStr">
@@ -9411,17 +9299,17 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Mat007</t>
+          <t>MAT-STD-001</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>紧固件标准包</t>
+          <t>总装标准件包</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
-          <t>AE-100-007</t>
+          <t>A1000-STD-001</t>
         </is>
       </c>
       <c r="F6" s="32" t="inlineStr">
@@ -9463,7 +9351,7 @@
       </c>
       <c r="Q6" s="32" t="inlineStr">
         <is>
-          <t>Mb001</t>
+          <t>MBOM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="R6" s="32" t="inlineStr">
@@ -9475,7 +9363,7 @@
     <row r="7">
       <c r="A7" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="B7" s="32" t="inlineStr">
@@ -9485,17 +9373,17 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Mat008</t>
+          <t>MAT-SEAL-001</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>密封垫组件</t>
+          <t>密封组件包</t>
         </is>
       </c>
       <c r="E7" s="32" t="inlineStr">
         <is>
-          <t>AE-100-008</t>
+          <t>A1000-SEAL-001</t>
         </is>
       </c>
       <c r="F7" s="32" t="inlineStr">
@@ -9537,7 +9425,7 @@
       </c>
       <c r="Q7" s="32" t="inlineStr">
         <is>
-          <t>Mb001</t>
+          <t>MBOM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="R7" s="32" t="inlineStr">
@@ -9547,78 +9435,24 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>Mat011</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>Mat012</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>发运包装组件</t>
-        </is>
-      </c>
-      <c r="E8" s="32" t="inlineStr">
-        <is>
-          <t>AE-100-012</t>
-        </is>
-      </c>
-      <c r="F8" s="32" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>配套件</t>
-        </is>
-      </c>
-      <c r="H8" s="32" t="inlineStr">
-        <is>
-          <t>外购件</t>
-        </is>
-      </c>
-      <c r="I8" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="32" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="K8" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="32" t="n">
-        <v>60</v>
-      </c>
+      <c r="A8" s="32" t="inlineStr"/>
+      <c r="B8" s="32" t="inlineStr"/>
+      <c r="C8" s="32" t="inlineStr"/>
+      <c r="D8" s="32" t="inlineStr"/>
+      <c r="E8" s="32" t="inlineStr"/>
+      <c r="F8" s="32" t="inlineStr"/>
+      <c r="G8" s="32" t="inlineStr"/>
+      <c r="H8" s="32" t="inlineStr"/>
+      <c r="I8" s="32" t="inlineStr"/>
+      <c r="J8" s="32" t="inlineStr"/>
+      <c r="K8" s="32" t="inlineStr"/>
+      <c r="L8" s="32" t="inlineStr"/>
       <c r="M8" s="32" t="inlineStr"/>
       <c r="N8" s="32" t="inlineStr"/>
       <c r="O8" s="32" t="inlineStr"/>
-      <c r="P8" s="32" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="Q8" s="32" t="inlineStr">
-        <is>
-          <t>Mb001</t>
-        </is>
-      </c>
-      <c r="R8" s="32" t="inlineStr">
-        <is>
-          <t>量产</t>
-        </is>
-      </c>
+      <c r="P8" s="32" t="inlineStr"/>
+      <c r="Q8" s="32" t="inlineStr"/>
+      <c r="R8" s="32" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="32" t="inlineStr"/>
@@ -11572,17 +11406,17 @@
     <row r="2">
       <c r="A2" s="32" t="inlineStr">
         <is>
-          <t>10-机加厂正式工艺</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="B2" s="32" t="inlineStr">
         <is>
-          <t>正式工艺</t>
+          <t>一级工艺</t>
         </is>
       </c>
       <c r="C2" s="32" t="inlineStr">
         <is>
-          <t>机加</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D2" s="32" t="inlineStr">
@@ -11592,7 +11426,7 @@
       </c>
       <c r="E2" s="32" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="F2" s="32" t="inlineStr">
@@ -11602,12 +11436,12 @@
       </c>
       <c r="G2" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="H2" s="32" t="inlineStr">
         <is>
-          <t>机加厂负责机匣件找正、机加和尺寸放行。</t>
+          <t>生产部一级工艺路线，用于一级工艺展开。</t>
         </is>
       </c>
       <c r="I2" s="32" t="inlineStr">
@@ -11617,14 +11451,14 @@
       </c>
       <c r="J2" s="32" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>20-盘轴厂正式工艺</t>
+          <t>机匣组件正式工艺</t>
         </is>
       </c>
       <c r="B3" s="32" t="inlineStr">
@@ -11644,7 +11478,7 @@
       </c>
       <c r="E3" s="32" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="F3" s="32" t="inlineStr">
@@ -11654,12 +11488,12 @@
       </c>
       <c r="G3" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="H3" s="32" t="inlineStr">
         <is>
-          <t>盘轴厂负责盘轴关键件复合加工、平衡修正和终检。</t>
+          <t>机加厂正式工艺。</t>
         </is>
       </c>
       <c r="I3" s="32" t="inlineStr">
@@ -11669,14 +11503,14 @@
       </c>
       <c r="J3" s="32" t="inlineStr">
         <is>
-          <t>Biz020</t>
+          <t>ORG-MC-001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
-          <t>30-叶片厂正式工艺</t>
+          <t>盘轴组件正式工艺</t>
         </is>
       </c>
       <c r="B4" s="32" t="inlineStr">
@@ -11686,7 +11520,7 @@
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>热表</t>
+          <t>机加</t>
         </is>
       </c>
       <c r="D4" s="32" t="inlineStr">
@@ -11696,7 +11530,7 @@
       </c>
       <c r="E4" s="32" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="F4" s="32" t="inlineStr">
@@ -11706,12 +11540,12 @@
       </c>
       <c r="G4" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="H4" s="32" t="inlineStr">
         <is>
-          <t>叶片厂负责叶片成型、涂层与叶片终检。</t>
+          <t>盘轴厂正式工艺。</t>
         </is>
       </c>
       <c r="I4" s="32" t="inlineStr">
@@ -11721,14 +11555,14 @@
       </c>
       <c r="J4" s="32" t="inlineStr">
         <is>
-          <t>Biz030</t>
+          <t>ORG-SH-001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
         <is>
-          <t>40-装配厂正式工艺</t>
+          <t>叶片组件套正式工艺</t>
         </is>
       </c>
       <c r="B5" s="32" t="inlineStr">
@@ -11738,7 +11572,7 @@
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>装配</t>
+          <t>热表</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
@@ -11748,7 +11582,7 @@
       </c>
       <c r="E5" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="F5" s="32" t="inlineStr">
@@ -11758,12 +11592,12 @@
       </c>
       <c r="G5" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="H5" s="32" t="inlineStr">
         <is>
-          <t>装配厂负责齐套确认、总装试车和整机交付放行。</t>
+          <t>叶片厂正式工艺。</t>
         </is>
       </c>
       <c r="I5" s="32" t="inlineStr">
@@ -11773,24 +11607,24 @@
       </c>
       <c r="J5" s="32" t="inlineStr">
         <is>
-          <t>Biz040</t>
+          <t>ORG-BL-001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
         <is>
-          <t>发动机一级协同工艺</t>
+          <t>装配厂正式工艺</t>
         </is>
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>一级工艺</t>
+          <t>正式工艺</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>装配</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
@@ -11800,7 +11634,7 @@
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="F6" s="32" t="inlineStr">
@@ -11810,12 +11644,12 @@
       </c>
       <c r="G6" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="H6" s="32" t="inlineStr">
         <is>
-          <t>生产部统一承接厂际协同计划，按参与工厂拆解一级工艺。</t>
+          <t>装配厂正式工艺路线，包含 OP10 装配准备、OP20 总装、OP30 完工装配。</t>
         </is>
       </c>
       <c r="I6" s="32" t="inlineStr">
@@ -11825,7 +11659,7 @@
       </c>
       <c r="J6" s="32" t="inlineStr">
         <is>
-          <t>Biz900</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
     </row>
@@ -13103,7 +12937,7 @@
     <row r="2">
       <c r="A2" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B2" s="32" t="inlineStr">
@@ -13113,12 +12947,12 @@
       </c>
       <c r="C2" s="32" t="inlineStr">
         <is>
-          <t>完成机匣毛坯上线、找正和工艺准备。</t>
+          <t>生产部协同机加厂完成机匣组件交付。</t>
         </is>
       </c>
       <c r="D2" s="32" t="inlineStr">
         <is>
-          <t>Wc101</t>
+          <t>WC-PD-MC-01</t>
         </is>
       </c>
       <c r="E2" s="32" t="inlineStr"/>
@@ -13129,14 +12963,14 @@
       </c>
       <c r="G2" s="32" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="H2" s="32" t="n">
         <v>10</v>
       </c>
       <c r="I2" s="32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2" s="32" t="inlineStr">
         <is>
@@ -13158,12 +12992,12 @@
       </c>
       <c r="N2" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="O2" s="32" t="inlineStr">
         <is>
-          <t>机匣毛坯上线与找正</t>
+          <t>10-机加厂</t>
         </is>
       </c>
       <c r="P2" s="32" t="inlineStr"/>
@@ -13176,7 +13010,7 @@
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B3" s="32" t="inlineStr">
@@ -13186,12 +13020,12 @@
       </c>
       <c r="C3" s="32" t="inlineStr">
         <is>
-          <t>完成机匣关键孔面、安装面和外形粗精加工。</t>
+          <t>生产部协同盘轴厂完成盘轴组件交付。</t>
         </is>
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>Wc101</t>
+          <t>WC-PD-SH-01</t>
         </is>
       </c>
       <c r="E3" s="32" t="inlineStr"/>
@@ -13202,14 +13036,14 @@
       </c>
       <c r="G3" s="32" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="H3" s="32" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I3" s="32" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J3" s="32" t="inlineStr">
         <is>
@@ -13231,12 +13065,12 @@
       </c>
       <c r="N3" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="O3" s="32" t="inlineStr">
         <is>
-          <t>机匣五轴粗精加工</t>
+          <t>20-盘轴厂</t>
         </is>
       </c>
       <c r="P3" s="32" t="inlineStr"/>
@@ -13249,22 +13083,22 @@
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>完成机匣尺寸、同轴度和表面质量终检。</t>
+          <t>生产部协同叶片厂完成叶片组件套交付。</t>
         </is>
       </c>
       <c r="D4" s="32" t="inlineStr">
         <is>
-          <t>Wc102</t>
+          <t>WC-PD-BL-01</t>
         </is>
       </c>
       <c r="E4" s="32" t="inlineStr"/>
@@ -13275,14 +13109,14 @@
       </c>
       <c r="G4" s="32" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="H4" s="32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I4" s="32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J4" s="32" t="inlineStr">
         <is>
@@ -13304,12 +13138,12 @@
       </c>
       <c r="N4" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="O4" s="32" t="inlineStr">
         <is>
-          <t>机匣尺寸终检</t>
+          <t>30-叶片厂</t>
         </is>
       </c>
       <c r="P4" s="32" t="inlineStr"/>
@@ -13322,7 +13156,7 @@
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B5" s="32" t="inlineStr">
@@ -13332,12 +13166,12 @@
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>完成盘轴类关键件车铣复合加工。</t>
+          <t>生产部协同装配厂完成总装试车与交付。</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>Wc201</t>
+          <t>WC-PD-AS-01</t>
         </is>
       </c>
       <c r="E5" s="32" t="inlineStr"/>
@@ -13348,7 +13182,7 @@
       </c>
       <c r="G5" s="32" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="H5" s="32" t="n">
@@ -13377,25 +13211,25 @@
       </c>
       <c r="N5" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="O5" s="32" t="inlineStr">
         <is>
-          <t>盘轴复合加工</t>
+          <t>40-装配厂</t>
         </is>
       </c>
       <c r="P5" s="32" t="inlineStr"/>
       <c r="Q5" s="32" t="inlineStr">
         <is>
-          <t>机械加工专业</t>
+          <t>装配专业</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="B6" s="32" t="inlineStr">
@@ -13405,12 +13239,12 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>完成盘轴动平衡检测与修正。</t>
+          <t>完成机匣毛坯装夹、粗加工与找正。</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>Wc202</t>
+          <t>WC-MC-01</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr"/>
@@ -13421,14 +13255,14 @@
       </c>
       <c r="G6" s="32" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="H6" s="32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J6" s="32" t="inlineStr">
         <is>
@@ -13450,12 +13284,12 @@
       </c>
       <c r="N6" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="O6" s="32" t="inlineStr">
         <is>
-          <t>盘轴动平衡修正</t>
+          <t>机匣粗加工</t>
         </is>
       </c>
       <c r="P6" s="32" t="inlineStr"/>
@@ -13468,22 +13302,22 @@
     <row r="7">
       <c r="A7" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>完成盘轴无损、尺寸和外观终检。</t>
+          <t>完成机匣关键孔面与装配基准精加工。</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>Wc203</t>
+          <t>WC-MC-01</t>
         </is>
       </c>
       <c r="E7" s="32" t="inlineStr"/>
@@ -13494,14 +13328,14 @@
       </c>
       <c r="G7" s="32" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="H7" s="32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J7" s="32" t="inlineStr">
         <is>
@@ -13523,12 +13357,12 @@
       </c>
       <c r="N7" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="O7" s="32" t="inlineStr">
         <is>
-          <t>盘轴终检放行</t>
+          <t>机匣精加工</t>
         </is>
       </c>
       <c r="P7" s="32" t="inlineStr"/>
@@ -13541,22 +13375,22 @@
     <row r="8">
       <c r="A8" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>加工</t>
+          <t>检验</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>完成叶片型面成型和冷端修整。</t>
+          <t>完成机匣组件尺寸终检与放行。</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>Wc301</t>
+          <t>WC-QC-MC-01</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr"/>
@@ -13567,14 +13401,14 @@
       </c>
       <c r="G8" s="32" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="H8" s="32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I8" s="32" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J8" s="32" t="inlineStr">
         <is>
@@ -13596,12 +13430,12 @@
       </c>
       <c r="N8" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="O8" s="32" t="inlineStr">
         <is>
-          <t>叶片成型加工</t>
+          <t>机匣终检</t>
         </is>
       </c>
       <c r="P8" s="32" t="inlineStr"/>
@@ -13614,7 +13448,7 @@
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="B9" s="32" t="inlineStr">
@@ -13624,12 +13458,12 @@
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>完成叶片保护涂层喷涂和固化。</t>
+          <t>完成盘轴毛坯复合加工。</t>
         </is>
       </c>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>Wc302</t>
+          <t>WC-SH-01</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr"/>
@@ -13640,14 +13474,14 @@
       </c>
       <c r="G9" s="32" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="H9" s="32" t="n">
         <v>12</v>
       </c>
       <c r="I9" s="32" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J9" s="32" t="inlineStr">
         <is>
@@ -13669,12 +13503,12 @@
       </c>
       <c r="N9" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="O9" s="32" t="inlineStr">
         <is>
-          <t>叶片表面涂层处理</t>
+          <t>盘轴加工</t>
         </is>
       </c>
       <c r="P9" s="32" t="inlineStr"/>
@@ -13687,22 +13521,22 @@
     <row r="10">
       <c r="A10" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>完成叶片型面、流道和外观终检。</t>
+          <t>完成盘轴组件动平衡与修正。</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>Wc303</t>
+          <t>WC-SH-01</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr"/>
@@ -13713,14 +13547,14 @@
       </c>
       <c r="G10" s="32" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="H10" s="32" t="n">
         <v>8</v>
       </c>
       <c r="I10" s="32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J10" s="32" t="inlineStr">
         <is>
@@ -13742,12 +13576,12 @@
       </c>
       <c r="N10" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="O10" s="32" t="inlineStr">
         <is>
-          <t>叶片终检放行</t>
+          <t>盘轴动平衡</t>
         </is>
       </c>
       <c r="P10" s="32" t="inlineStr"/>
@@ -13760,22 +13594,22 @@
     <row r="11">
       <c r="A11" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>加工</t>
+          <t>检验</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>完成机匣件、盘轴模块、叶片组件和装配配套件齐套确认。</t>
+          <t>完成盘轴组件终检与放行。</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>Wc401</t>
+          <t>WC-QC-SH-01</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr"/>
@@ -13786,14 +13620,14 @@
       </c>
       <c r="G11" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="H11" s="32" t="n">
         <v>8</v>
       </c>
       <c r="I11" s="32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J11" s="32" t="inlineStr">
         <is>
@@ -13815,25 +13649,25 @@
       </c>
       <c r="N11" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="O11" s="32" t="inlineStr">
         <is>
-          <t>齐套确认</t>
+          <t>盘轴终检</t>
         </is>
       </c>
       <c r="P11" s="32" t="inlineStr"/>
       <c r="Q11" s="32" t="inlineStr">
         <is>
-          <t>装配专业</t>
+          <t>机械加工专业</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="B12" s="32" t="inlineStr">
@@ -13843,12 +13677,12 @@
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>完成发动机核心机、盘轴和叶片相关总装联接。</t>
+          <t>完成叶片毛坯成型与修整。</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>Wc401</t>
+          <t>WC-BL-01</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr"/>
@@ -13859,14 +13693,14 @@
       </c>
       <c r="G12" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="H12" s="32" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I12" s="32" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J12" s="32" t="inlineStr">
         <is>
@@ -13888,40 +13722,40 @@
       </c>
       <c r="N12" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="O12" s="32" t="inlineStr">
         <is>
-          <t>整机总装</t>
+          <t>叶片成型</t>
         </is>
       </c>
       <c r="P12" s="32" t="inlineStr"/>
       <c r="Q12" s="32" t="inlineStr">
         <is>
-          <t>装配专业</t>
+          <t>机械加工专业</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>完成整机试车、质量结论和交付放行。</t>
+          <t>完成叶片保护涂层处理。</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>Wc402</t>
+          <t>WC-BL-01</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr"/>
@@ -13932,7 +13766,7 @@
       </c>
       <c r="G13" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="H13" s="32" t="n">
@@ -13961,40 +13795,40 @@
       </c>
       <c r="N13" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="O13" s="32" t="inlineStr">
         <is>
-          <t>整机试车与交付放行</t>
+          <t>叶片涂层</t>
         </is>
       </c>
       <c r="P13" s="32" t="inlineStr"/>
       <c r="Q13" s="32" t="inlineStr">
         <is>
-          <t>装配专业</t>
+          <t>机械加工专业</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>加工</t>
+          <t>检验</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>生产部确认机加厂机匣件完工与交付节拍。</t>
+          <t>完成叶片组件套终检与放行。</t>
         </is>
       </c>
       <c r="D14" s="32" t="inlineStr">
         <is>
-          <t>Wc901</t>
+          <t>WC-QC-BL-01</t>
         </is>
       </c>
       <c r="E14" s="32" t="inlineStr"/>
@@ -14005,14 +13839,14 @@
       </c>
       <c r="G14" s="32" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="H14" s="32" t="n">
         <v>8</v>
       </c>
       <c r="I14" s="32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J14" s="32" t="inlineStr">
         <is>
@@ -14034,12 +13868,12 @@
       </c>
       <c r="N14" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="O14" s="32" t="inlineStr">
         <is>
-          <t>10-机加厂阶段完成</t>
+          <t>叶片终检</t>
         </is>
       </c>
       <c r="P14" s="32" t="inlineStr"/>
@@ -14052,7 +13886,7 @@
     <row r="15">
       <c r="A15" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
@@ -14062,12 +13896,12 @@
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>生产部确认盘轴厂关键转子模块完工与交付节拍。</t>
+          <t>完成装配准备与齐套确认。</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>Wc902</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr"/>
@@ -14078,14 +13912,14 @@
       </c>
       <c r="G15" s="32" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="H15" s="32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I15" s="32" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J15" s="32" t="inlineStr">
         <is>
@@ -14107,25 +13941,25 @@
       </c>
       <c r="N15" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="O15" s="32" t="inlineStr">
         <is>
-          <t>20-盘轴厂阶段完成</t>
+          <t>装配准备</t>
         </is>
       </c>
       <c r="P15" s="32" t="inlineStr"/>
       <c r="Q15" s="32" t="inlineStr">
         <is>
-          <t>机械加工专业</t>
+          <t>装配专业</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="B16" s="32" t="inlineStr">
@@ -14135,12 +13969,12 @@
       </c>
       <c r="C16" s="32" t="inlineStr">
         <is>
-          <t>生产部确认叶片厂关键叶片组件完工与交付节拍。</t>
+          <t>完成发动机总装联接。</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>Wc903</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr"/>
@@ -14151,14 +13985,14 @@
       </c>
       <c r="G16" s="32" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="H16" s="32" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I16" s="32" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J16" s="32" t="inlineStr">
         <is>
@@ -14180,25 +14014,25 @@
       </c>
       <c r="N16" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="O16" s="32" t="inlineStr">
         <is>
-          <t>30-叶片厂阶段完成</t>
+          <t>总装</t>
         </is>
       </c>
       <c r="P16" s="32" t="inlineStr"/>
       <c r="Q16" s="32" t="inlineStr">
         <is>
-          <t>机械加工专业</t>
+          <t>装配专业</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="B17" s="32" t="inlineStr">
@@ -14208,12 +14042,12 @@
       </c>
       <c r="C17" s="32" t="inlineStr">
         <is>
-          <t>生产部确认总装、试车和交付窗口，形成整机交付承诺。</t>
+          <t>完成完工装配、试车前状态确认与入库前准备。</t>
         </is>
       </c>
       <c r="D17" s="32" t="inlineStr">
         <is>
-          <t>Wc904</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr"/>
@@ -14224,14 +14058,14 @@
       </c>
       <c r="G17" s="32" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-ENG-001</t>
         </is>
       </c>
       <c r="H17" s="32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I17" s="32" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J17" s="32" t="inlineStr">
         <is>
@@ -14253,12 +14087,12 @@
       </c>
       <c r="N17" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="O17" s="32" t="inlineStr">
         <is>
-          <t>40-装配厂总装试车完成</t>
+          <t>完工装配</t>
         </is>
       </c>
       <c r="P17" s="32" t="inlineStr"/>
@@ -15934,12 +15768,12 @@
       </c>
       <c r="B2" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C2" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D2" s="32" t="inlineStr">
@@ -15949,7 +15783,7 @@
       </c>
       <c r="E2" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -15961,12 +15795,12 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D3" s="32" t="inlineStr">
@@ -15976,7 +15810,7 @@
       </c>
       <c r="E3" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -15988,12 +15822,12 @@
       </c>
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D4" s="32" t="inlineStr">
@@ -16003,7 +15837,7 @@
       </c>
       <c r="E4" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -16015,12 +15849,12 @@
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
@@ -16030,7 +15864,7 @@
       </c>
       <c r="E5" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -16042,12 +15876,12 @@
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
@@ -16057,7 +15891,7 @@
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -16069,12 +15903,12 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
@@ -16084,7 +15918,7 @@
       </c>
       <c r="E7" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -16096,12 +15930,12 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
@@ -16111,7 +15945,7 @@
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -16123,12 +15957,12 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D9" s="32" t="inlineStr">
@@ -16138,7 +15972,7 @@
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -16150,12 +15984,12 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
@@ -16165,7 +15999,7 @@
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -16177,12 +16011,12 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
@@ -16192,7 +16026,7 @@
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -16204,12 +16038,12 @@
       </c>
       <c r="B12" s="32" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
@@ -16219,7 +16053,7 @@
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
     </row>
@@ -16913,7 +16747,7 @@
       </c>
       <c r="B2" s="32" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="C2" s="32" t="inlineStr">
@@ -16923,12 +16757,12 @@
       </c>
       <c r="D2" s="32" t="inlineStr">
         <is>
-          <t>Mat001</t>
+          <t>MAT-CAS-BLANK-001</t>
         </is>
       </c>
       <c r="E2" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="F2" s="32" t="n">
@@ -16943,7 +16777,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
@@ -16953,12 +16787,12 @@
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>Mat003</t>
+          <t>MAT-SHAFT-BLANK-001</t>
         </is>
       </c>
       <c r="E3" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="F3" s="32" t="n">
@@ -16973,7 +16807,7 @@
       </c>
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="C4" s="32" t="inlineStr">
@@ -16983,12 +16817,12 @@
       </c>
       <c r="D4" s="32" t="inlineStr">
         <is>
-          <t>Mat005</t>
+          <t>MAT-BLADE-BLANK-001</t>
         </is>
       </c>
       <c r="E4" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="F4" s="32" t="n">
@@ -17003,7 +16837,7 @@
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17013,12 +16847,12 @@
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>Mat009</t>
+          <t>MAT-COAT-001</t>
         </is>
       </c>
       <c r="E5" s="32" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP20</t>
         </is>
       </c>
       <c r="F5" s="32" t="n">
@@ -17033,7 +16867,7 @@
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17043,12 +16877,12 @@
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="F6" s="32" t="n">
@@ -17063,7 +16897,7 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17073,12 +16907,12 @@
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="E7" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="F7" s="32" t="n">
@@ -17093,7 +16927,7 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17103,16 +16937,16 @@
       </c>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="F8" s="32" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -17123,7 +16957,7 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17133,12 +16967,12 @@
       </c>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>Mat007</t>
+          <t>MAT-STD-001</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="F9" s="32" t="n">
@@ -17153,7 +16987,7 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17163,12 +16997,12 @@
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>Mat008</t>
+          <t>MAT-SEAL-001</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP30</t>
         </is>
       </c>
       <c r="F10" s="32" t="n">
@@ -17176,64 +17010,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>Rt040</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>Mat010</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>0030</t>
-        </is>
-      </c>
-      <c r="F11" s="32" t="n">
-        <v>1</v>
-      </c>
+      <c r="A11" s="32" t="inlineStr"/>
+      <c r="B11" s="32" t="inlineStr"/>
+      <c r="C11" s="32" t="inlineStr"/>
+      <c r="D11" s="32" t="inlineStr"/>
+      <c r="E11" s="32" t="inlineStr"/>
+      <c r="F11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>Rt040</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>Mat012</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>0030</t>
-        </is>
-      </c>
-      <c r="F12" s="32" t="n">
-        <v>1</v>
-      </c>
+      <c r="A12" s="32" t="inlineStr"/>
+      <c r="B12" s="32" t="inlineStr"/>
+      <c r="C12" s="32" t="inlineStr"/>
+      <c r="D12" s="32" t="inlineStr"/>
+      <c r="E12" s="32" t="inlineStr"/>
+      <c r="F12" s="32" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="32" t="inlineStr"/>
